--- a/monitor_xlsx/20260202.xlsx
+++ b/monitor_xlsx/20260202.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,9 @@
     <font>
       <color rgb="00008000"/>
     </font>
+    <font>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -132,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -195,6 +198,7 @@
       <alignment horizontal="general"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1170,7 +1174,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2659,6 +2663,112 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>914</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2309</v>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>412</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1413</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-580</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1575</v>
+      </c>
+      <c r="J22" t="n">
+        <v>129</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2409</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11965</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-47606</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1140</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>269</v>
+      </c>
+      <c r="G23" t="n">
+        <v>410</v>
+      </c>
+      <c r="H23" t="n">
+        <v>216</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-925</v>
+      </c>
+      <c r="J23" t="n">
+        <v>74</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2642</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13218</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-140179</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260202.xlsx
+++ b/monitor_xlsx/20260202.xlsx
@@ -1174,7 +1174,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2769,6 +2769,59 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>962</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>826</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G24" t="n">
+        <v>304</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-50</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-79</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>主力積極買進</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260202.xlsx
+++ b/monitor_xlsx/20260202.xlsx
@@ -1174,7 +1174,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2822,6 +2822,59 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4570</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-234</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-80</v>
+      </c>
+      <c r="J25" t="n">
+        <v>26</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6246</v>
+      </c>
+      <c r="L25" t="n">
+        <v>32824</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-58788</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
